--- a/branches/1.0.0/ValueSet-mii-vs-sdd-einkommen.xlsx
+++ b/branches/1.0.0/ValueSet-mii-vs-sdd-einkommen.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-08T12:47:32+00:00</t>
+    <t>2026-09-14T12:30:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
